--- a/Models/Яйца/results/Яйца - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4533.82</v>
+        <v>2946.41</v>
       </c>
       <c r="C2" t="n">
-        <v>4015.63</v>
+        <v>2524.14</v>
       </c>
       <c r="D2" t="n">
-        <v>6.72</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1278.08</v>
+        <v>1580.75</v>
       </c>
       <c r="C3" t="n">
-        <v>1138.98</v>
+        <v>1465.02</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5477.22</v>
+        <v>4030.44</v>
       </c>
       <c r="C4" t="n">
-        <v>5060.42</v>
+        <v>3685.44</v>
       </c>
       <c r="D4" t="n">
-        <v>11.34</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1424.04</v>
+        <v>816</v>
       </c>
       <c r="C5" t="n">
-        <v>1302.33</v>
+        <v>752.8099999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>60.52</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>388.4</v>
+        <v>359.73</v>
       </c>
       <c r="C6" t="n">
-        <v>348.57</v>
+        <v>313.61</v>
       </c>
       <c r="D6" t="n">
-        <v>6.32</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>2.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>16.11</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="C8" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="D8" t="n">
-        <v>89.75</v>
+        <v>104.96</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1539.5</v>
+        <v>2834.03</v>
       </c>
       <c r="C9" t="n">
-        <v>1373.4</v>
+        <v>2546.49</v>
       </c>
       <c r="D9" t="n">
-        <v>8.99</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2114.02</v>
+        <v>1460.24</v>
       </c>
       <c r="C10" t="n">
-        <v>1941.3</v>
+        <v>1383.31</v>
       </c>
       <c r="D10" t="n">
-        <v>18.91</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>965.09</v>
+        <v>864</v>
       </c>
       <c r="C11" t="n">
-        <v>859.96</v>
+        <v>746.92</v>
       </c>
       <c r="D11" t="n">
-        <v>6.9</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3311.3</v>
+        <v>3676.45</v>
       </c>
       <c r="C12" t="n">
-        <v>3057.4</v>
+        <v>3295.89</v>
       </c>
       <c r="D12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6680.38</v>
+        <v>5688.23</v>
       </c>
       <c r="C13" t="n">
-        <v>6018.95</v>
+        <v>4990.36</v>
       </c>
       <c r="D13" t="n">
-        <v>19.18</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47.05</v>
+        <v>42.59</v>
       </c>
       <c r="C14" t="n">
-        <v>39.28</v>
+        <v>38.62</v>
       </c>
       <c r="D14" t="n">
-        <v>6.51</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.89</v>
+        <v>1.78</v>
       </c>
       <c r="C15" t="n">
-        <v>4.99</v>
+        <v>1.64</v>
       </c>
       <c r="D15" t="n">
-        <v>8.42</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>678.95</v>
+        <v>616.98</v>
       </c>
       <c r="C16" t="n">
-        <v>601.23</v>
+        <v>537.52</v>
       </c>
       <c r="D16" t="n">
-        <v>12.75</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2869.7</v>
+        <v>2601.47</v>
       </c>
       <c r="C17" t="n">
-        <v>2634.28</v>
+        <v>2396.53</v>
       </c>
       <c r="D17" t="n">
-        <v>9.390000000000001</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>278.15</v>
+        <v>885.89</v>
       </c>
       <c r="C18" t="n">
-        <v>243.45</v>
+        <v>785.8</v>
       </c>
       <c r="D18" t="n">
-        <v>20.19</v>
+        <v>37.34</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>933.23</v>
+        <v>902.6</v>
       </c>
       <c r="C19" t="n">
-        <v>844.77</v>
+        <v>806.74</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7085.82</v>
+        <v>3402.68</v>
       </c>
       <c r="C20" t="n">
-        <v>6418.42</v>
+        <v>3136.65</v>
       </c>
       <c r="D20" t="n">
-        <v>12.68</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2328.95</v>
+        <v>1594.81</v>
       </c>
       <c r="C21" t="n">
-        <v>2081.51</v>
+        <v>1368.09</v>
       </c>
       <c r="D21" t="n">
-        <v>10.77</v>
+        <v>6.22</v>
       </c>
     </row>
   </sheetData>
